--- a/development/rocksdb/self_RD/saved01/max_open_file_1/structured_log_data.xlsx
+++ b/development/rocksdb/self_RD/saved01/max_open_file_1/structured_log_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>fixed #PQ = 5000 point_query_time_on_currently_deleted_all_ns</t>
+          <t>fixed #PQ = 100000 point_query_time_on_currently_deleted_all_ns</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -477,81 +477,837 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19488512526</v>
+        <v>2888744590</v>
       </c>
       <c r="C2" t="n">
-        <v>5895754</v>
+        <v>4922495</v>
       </c>
       <c r="D2" t="n">
-        <v>3987000</v>
+        <v>5000000</v>
       </c>
       <c r="E2" t="n">
-        <v>12999000</v>
+        <v>11000000</v>
       </c>
       <c r="F2" t="n">
-        <v>8617191043</v>
+        <v>108547878430</v>
       </c>
       <c r="G2" t="n">
-        <v>1978496039</v>
+        <v>48260230326</v>
       </c>
       <c r="H2" t="n">
-        <v>260384278556</v>
+        <v>1946873442652</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log2112</t>
+          <t>log2211</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19510919633</v>
+        <v>2929566493</v>
       </c>
       <c r="C3" t="n">
-        <v>5895767</v>
+        <v>5019419</v>
       </c>
       <c r="D3" t="n">
-        <v>6999000</v>
+        <v>5000000</v>
       </c>
       <c r="E3" t="n">
-        <v>12998000</v>
+        <v>12000000</v>
       </c>
       <c r="F3" t="n">
-        <v>8077058837</v>
+        <v>106007345538</v>
       </c>
       <c r="G3" t="n">
-        <v>1932765469</v>
+        <v>31511096461</v>
       </c>
       <c r="H3" t="n">
-        <v>256505913458</v>
+        <v>1942909088815</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>log2311</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2880245336</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4861736</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10999000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>107853583963</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1293987795</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1926850250655</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>log2411</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2786279517</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5034357</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8998000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>106703178763</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1063913659</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2040114406391</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>log2511</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2803051553</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5181313</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6001000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10999000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>105924768057</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31443446713</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1978497483828</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>log2611</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2869552013</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5177688</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7001000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>110194788021</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1943608056</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1935837462676</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>log2711</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2796675804</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4932056</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>108663649649</v>
+      </c>
+      <c r="G8" t="n">
+        <v>34677283368</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2158511804093</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>log2811</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2808067153</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4868801</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4999000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10999000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>107186719766</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3884698092</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1951267587189</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>log2911</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2896150986</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4960034</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>105404161383</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34411113097</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1992673884446</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>log3011</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2896340963</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4977362</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7001000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>111615784364</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3726470168</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2051623282560</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>log2112</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2929867734</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4846694</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11999000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>99026562279</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50100604366</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1921795168749</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>log2212</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2770681042</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4931638</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>90022441651</v>
+      </c>
+      <c r="G13" t="n">
+        <v>32825749668</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1881822437300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>log2312</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2792630008</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5114637</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>94757059730</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1182565610</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1887283412418</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>log2412</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3060883333</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4490461</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7999000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11999000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>95680822901</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1034488676</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10765213393041</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>log2512</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3192934667</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5150796</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>94087406119</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35284691754</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1951486182831</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>log2612</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3087299289</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5175863</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>93735188054</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1922384966</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1871937431628</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>log2712</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2878924656</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5050320</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7999000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11999000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>95397456773</v>
+      </c>
+      <c r="G18" t="n">
+        <v>36827901288</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1958286609836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>log2812</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2714307448</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4902932</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10999000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>97232867963</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3022103849</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1908035703748</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>log2912</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2783771728</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4891794</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6001000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>95415788440</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35962207176</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1968561834050</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>log3012</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2835373432</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4995731</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5998000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10999000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>109528095570</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2524348105</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2102776790211</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>log2113</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>19827097324</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5841043</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B22" t="n">
+        <v>2929667604</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4948367</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8996000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11996000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>81383284978</v>
+      </c>
+      <c r="G22" t="n">
+        <v>47677471956</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1874125944262</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>log2213</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2823767846</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5036129</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>73822057041</v>
+      </c>
+      <c r="G23" t="n">
+        <v>26256492267</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1851058107916</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>log2313</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2735973329</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4961814</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7001000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>72188679754</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1133050652</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1833050394788</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>log2413</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2751386529</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4964158</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>74607817058</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1008379467</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1840814174984</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>log2513</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3014806904</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5051276</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>74677611654</v>
+      </c>
+      <c r="G26" t="n">
+        <v>29130629822</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1869651216641</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>log2613</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2810993918</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4927862</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4998000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10999000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>78708011427</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2855588969</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1913820660474</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>log2713</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2763589687</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5003456</v>
+      </c>
+      <c r="D28" t="n">
         <v>4000000</v>
       </c>
-      <c r="E4" t="n">
-        <v>12998000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7901032710</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1516883270</v>
-      </c>
-      <c r="H4" t="n">
-        <v>255062027861</v>
+      <c r="E28" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>70165649789</v>
+      </c>
+      <c r="G28" t="n">
+        <v>28612374003</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1849236558282</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>log2813</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2846462749</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5053013</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>77015249456</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4065176163</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1896870166488</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>log2913</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2935309251</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5068675</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F30" t="n">
+        <v>74026264520</v>
+      </c>
+      <c r="G30" t="n">
+        <v>30732601195</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1916709778358</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>log3013</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2741414719</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5073685</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3999000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10999000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>76870373892</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3581872008</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1829554248432</v>
       </c>
     </row>
   </sheetData>
